--- a/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0003T0006Z000C1N28_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0003T0006Z000C1N28_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>23.1948270094864</v>
+        <v>3.76915938904154</v>
       </c>
       <c r="D2" t="n">
-        <v>51.41984052872976</v>
+        <v>8.355724085918586</v>
       </c>
       <c r="E2" t="n">
-        <v>17.38343773867943</v>
+        <v>2.824808632535408</v>
       </c>
       <c r="F2" t="n">
-        <v>11.00855629141242</v>
+        <v>1.788890397354518</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>35.65459297201414</v>
+        <v>5.793871357952297</v>
       </c>
       <c r="D3" t="n">
-        <v>78.38353259991189</v>
+        <v>12.73732404748568</v>
       </c>
       <c r="E3" t="n">
-        <v>17.38343773867943</v>
+        <v>2.824808632535408</v>
       </c>
       <c r="F3" t="n">
-        <v>11.00855629141242</v>
+        <v>1.788890397354518</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>64.68649182866547</v>
+        <v>10.51155492215814</v>
       </c>
       <c r="D4" t="n">
-        <v>64.643065773907</v>
+        <v>10.50449818825989</v>
       </c>
       <c r="E4" t="n">
-        <v>17.38343773867943</v>
+        <v>2.824808632535408</v>
       </c>
       <c r="F4" t="n">
-        <v>11.00855629141242</v>
+        <v>1.788890397354518</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
